--- a/data/raw/medicamentosHU2.xlsx
+++ b/data/raw/medicamentosHU2.xlsx
@@ -585,11 +585,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>678319200000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1699460637000</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30/06/91</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>08/11/23</t>
+        </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -683,11 +687,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>880930800000</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1699460638000</v>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30/11/97</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>08/11/23</t>
+        </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -781,11 +789,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>678319200000</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1699460630000</v>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30/06/91</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>08/11/23</t>
+        </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -879,8 +891,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>-213152400000</v>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>31/03/63</t>
+        </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
@@ -975,8 +989,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>1178488800000</v>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>06/05/07</t>
+        </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
@@ -1071,8 +1087,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>1178488800000</v>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>06/05/07</t>
+        </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
@@ -1167,8 +1185,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>1425337200000</v>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>02/03/15</t>
+        </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
@@ -1263,8 +1283,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>1425337200000</v>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>02/03/15</t>
+        </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
@@ -1359,8 +1381,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>1188856800000</v>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>03/09/07</t>
+        </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
@@ -1455,8 +1479,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>1188856800000</v>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>03/09/07</t>
+        </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
@@ -1551,8 +1577,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>1464624600000</v>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30/05/16</t>
+        </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
@@ -1647,8 +1675,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>1464559200000</v>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>29/05/16</t>
+        </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
@@ -1743,8 +1773,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>1468965600000</v>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>19/07/16</t>
+        </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
@@ -1839,8 +1871,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>1468965600000</v>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>19/07/16</t>
+        </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
@@ -1935,8 +1969,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>1480892400000</v>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>04/12/16</t>
+        </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
@@ -2031,8 +2067,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>1480892400000</v>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>04/12/16</t>
+        </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
@@ -2127,8 +2165,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>1015801200000</v>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10/03/02</t>
+        </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
@@ -2223,8 +2263,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>1015801200000</v>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10/03/02</t>
+        </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
@@ -2319,8 +2361,10 @@
           <t>COLIRIO DE LIBERACION PROLONGADA</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>1096322400000</v>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>27/09/04</t>
+        </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
@@ -2415,8 +2459,10 @@
           <t>COLIRIO DE LIBERACION PROLONGADA</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>1096322400000</v>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>27/09/04</t>
+        </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
@@ -2511,8 +2557,10 @@
           <t>COLIRIO DE LIBERACION PROLONGADA</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>1269385200000</v>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>23/03/10</t>
+        </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
@@ -2607,8 +2655,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I23" t="n">
-        <v>1298242800000</v>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20/02/11</t>
+        </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
@@ -2703,8 +2753,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I24" t="n">
-        <v>1298242800000</v>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20/02/11</t>
+        </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
@@ -2799,8 +2851,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I25" t="n">
-        <v>1298242800000</v>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20/02/11</t>
+        </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
@@ -2895,8 +2949,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I26" t="n">
-        <v>1298242800000</v>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20/02/11</t>
+        </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
@@ -2991,8 +3047,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I27" t="n">
-        <v>1298242800000</v>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20/02/11</t>
+        </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
@@ -3087,8 +3145,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I28" t="n">
-        <v>1222380000000</v>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>25/09/08</t>
+        </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
@@ -3183,8 +3243,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I29" t="n">
-        <v>1222380000000</v>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>25/09/08</t>
+        </is>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
@@ -3279,8 +3341,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I30" t="n">
-        <v>1222380000000</v>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>25/09/08</t>
+        </is>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
@@ -3375,8 +3439,10 @@
           <t>CAPSULA LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I31" t="n">
-        <v>1048546800000</v>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>24/03/03</t>
+        </is>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
@@ -3471,8 +3537,10 @@
           <t>CAPSULA LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I32" t="n">
-        <v>1048114800000</v>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>19/03/03</t>
+        </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
@@ -3567,8 +3635,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I33" t="n">
-        <v>1302732000000</v>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>13/04/11</t>
+        </is>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
@@ -3663,8 +3733,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I34" t="n">
-        <v>372034800000</v>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15/10/81</t>
+        </is>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
@@ -3759,8 +3831,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I35" t="n">
-        <v>497574000000</v>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>07/10/85</t>
+        </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
@@ -3855,8 +3929,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I36" t="n">
-        <v>1443105399000</v>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>24/09/15</t>
+        </is>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
@@ -3951,8 +4027,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I37" t="n">
-        <v>1443105401000</v>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>24/09/15</t>
+        </is>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
@@ -4047,11 +4125,15 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I38" t="n">
-        <v>1287957600000</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1696403843000</v>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>24/10/10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>04/10/23</t>
+        </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -4145,8 +4227,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I39" t="n">
-        <v>1359933061000</v>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>03/02/13</t>
+        </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
@@ -4241,8 +4325,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I40" t="n">
-        <v>1359933044000</v>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>03/02/13</t>
+        </is>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
@@ -4337,8 +4423,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I41" t="n">
-        <v>1359933041000</v>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>03/02/13</t>
+        </is>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
@@ -4433,8 +4521,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I42" t="n">
-        <v>1359933037000</v>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>03/02/13</t>
+        </is>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
@@ -4529,8 +4619,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I43" t="n">
-        <v>1452770196000</v>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>14/01/16</t>
+        </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
@@ -4625,8 +4717,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I44" t="n">
-        <v>1452770194000</v>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>14/01/16</t>
+        </is>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
@@ -4721,8 +4815,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I45" t="n">
-        <v>1452770197000</v>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>14/01/16</t>
+        </is>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
@@ -4817,8 +4913,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I46" t="n">
-        <v>1312408800000</v>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>03/08/11</t>
+        </is>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
@@ -4913,8 +5011,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I47" t="n">
-        <v>1312408800000</v>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>03/08/11</t>
+        </is>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
@@ -5009,8 +5109,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I48" t="n">
-        <v>1312322400000</v>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>02/08/11</t>
+        </is>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
@@ -5105,8 +5207,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I49" t="n">
-        <v>959551200000</v>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>28/05/00</t>
+        </is>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
@@ -5185,7 +5289,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Viatris Pharmaceuticals S.L.U.</t>
+          <t>Viatris Pharmaceuticals S.L.</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -5201,8 +5305,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I50" t="n">
-        <v>925509600000</v>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>30/04/99</t>
+        </is>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
@@ -5281,7 +5387,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Viatris Pharmaceuticals S.L.U.</t>
+          <t>Viatris Pharmaceuticals S.L.</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -5297,8 +5403,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I51" t="n">
-        <v>925509600000</v>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>30/04/99</t>
+        </is>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
@@ -5393,8 +5501,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I52" t="n">
-        <v>1105484400000</v>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>11/01/05</t>
+        </is>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
@@ -5489,8 +5599,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I53" t="n">
-        <v>1215381600000</v>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>06/07/08</t>
+        </is>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
@@ -5585,8 +5697,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I54" t="n">
-        <v>1069110000000</v>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>17/11/03</t>
+        </is>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
@@ -5681,8 +5795,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I55" t="n">
-        <v>1215381600000</v>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>06/07/08</t>
+        </is>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
@@ -5777,8 +5893,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I56" t="n">
-        <v>907192800000</v>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>30/09/98</t>
+        </is>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
@@ -5873,8 +5991,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I57" t="n">
-        <v>1111446000000</v>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>21/03/05</t>
+        </is>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
@@ -5969,8 +6089,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I58" t="n">
-        <v>1232492400000</v>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>20/01/09</t>
+        </is>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
@@ -6065,8 +6187,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I59" t="n">
-        <v>1069110000000</v>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>17/11/03</t>
+        </is>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
@@ -6161,8 +6285,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I60" t="n">
-        <v>1232492400000</v>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>20/01/09</t>
+        </is>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
@@ -6257,11 +6383,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I61" t="n">
-        <v>646783200000</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1753108997000</v>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>30/06/90</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>21/07/25</t>
+        </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -6355,8 +6485,10 @@
           <t>CAPSULA LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I62" t="n">
-        <v>1369951200000</v>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>30/05/13</t>
+        </is>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
@@ -6451,8 +6583,10 @@
           <t>CAPSULA LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I63" t="n">
-        <v>1369951200000</v>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>30/05/13</t>
+        </is>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
@@ -6547,8 +6681,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I64" t="n">
-        <v>641512800000</v>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>30/04/90</t>
+        </is>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
@@ -6643,8 +6779,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I65" t="n">
-        <v>730940400000</v>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>28/02/93</t>
+        </is>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
@@ -6739,8 +6877,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I66" t="n">
-        <v>1188424800000</v>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>29/08/07</t>
+        </is>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
@@ -6835,8 +6975,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I67" t="n">
-        <v>1336428000000</v>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>07/05/12</t>
+        </is>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
@@ -6931,8 +7073,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I68" t="n">
-        <v>1154037600000</v>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>27/07/06</t>
+        </is>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
@@ -7027,8 +7171,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I69" t="n">
-        <v>1326668400000</v>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>15/01/12</t>
+        </is>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
@@ -7123,8 +7269,10 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I70" t="n">
-        <v>673048800000</v>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>30/04/91</t>
+        </is>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
@@ -7219,8 +7367,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I71" t="n">
-        <v>979772400000</v>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>17/01/01</t>
+        </is>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
@@ -7315,11 +7465,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I72" t="n">
-        <v>963784800000</v>
-      </c>
-      <c r="J72" t="n">
-        <v>1768393391000</v>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>16/07/00</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>14/01/26</t>
+        </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -7413,8 +7567,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I73" t="n">
-        <v>928188000000</v>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>31/05/99</t>
+        </is>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
@@ -7509,8 +7665,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I74" t="n">
-        <v>928188000000</v>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>31/05/99</t>
+        </is>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
@@ -7605,8 +7763,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I75" t="n">
-        <v>1065564000000</v>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>07/10/03</t>
+        </is>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
@@ -7701,8 +7861,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I76" t="n">
-        <v>1300316400000</v>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>16/03/11</t>
+        </is>
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
@@ -7797,8 +7959,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I77" t="n">
-        <v>1213826400000</v>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>18/06/08</t>
+        </is>
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
@@ -7893,8 +8057,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I78" t="n">
-        <v>1038956400000</v>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>03/12/02</t>
+        </is>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
@@ -7989,8 +8155,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I79" t="n">
-        <v>1315260000000</v>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>05/09/11</t>
+        </is>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
@@ -8085,8 +8253,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I80" t="n">
-        <v>1454540400000</v>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>03/02/16</t>
+        </is>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
@@ -8132,7 +8302,7 @@
         <v>1</v>
       </c>
       <c r="W80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X80" t="n">
         <v>559</v>
@@ -8181,8 +8351,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I81" t="n">
-        <v>1454540400000</v>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>03/02/16</t>
+        </is>
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
@@ -8228,7 +8400,7 @@
         <v>1</v>
       </c>
       <c r="W81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X81" t="n">
         <v>559</v>
@@ -8277,8 +8449,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I82" t="n">
-        <v>1306965600000</v>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>01/06/11</t>
+        </is>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
@@ -8373,8 +8547,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I83" t="n">
-        <v>1306965600000</v>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>01/06/11</t>
+        </is>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
@@ -8469,8 +8645,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I84" t="n">
-        <v>1317765600000</v>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>04/10/11</t>
+        </is>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
@@ -8565,8 +8743,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I85" t="n">
-        <v>1386802800000</v>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>11/12/13</t>
+        </is>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
@@ -8661,8 +8841,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I86" t="n">
-        <v>1145570400000</v>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>20/04/06</t>
+        </is>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
@@ -8757,8 +8939,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I87" t="n">
-        <v>1145484000000</v>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>19/04/06</t>
+        </is>
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
@@ -8853,8 +9037,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I88" t="n">
-        <v>1283724000000</v>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>05/09/10</t>
+        </is>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
@@ -8949,8 +9135,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I89" t="n">
-        <v>1286316000000</v>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>05/10/10</t>
+        </is>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
@@ -9045,8 +9233,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I90" t="n">
-        <v>1114552800000</v>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>26/04/05</t>
+        </is>
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
@@ -9141,8 +9331,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I91" t="n">
-        <v>1221602400000</v>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>16/09/08</t>
+        </is>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
@@ -9237,8 +9429,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I92" t="n">
-        <v>1076281200000</v>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>08/02/04</t>
+        </is>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
@@ -9333,8 +9527,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I93" t="n">
-        <v>928188000000</v>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>31/05/99</t>
+        </is>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
@@ -9429,11 +9625,15 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I94" t="n">
-        <v>1303855200000</v>
-      </c>
-      <c r="J94" t="n">
-        <v>1661785719000</v>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>26/04/11</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>29/08/22</t>
+        </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -9527,8 +9727,10 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I95" t="n">
-        <v>1266274800000</v>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>15/02/10</t>
+        </is>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
@@ -9623,11 +9825,15 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I96" t="n">
-        <v>1424369353000</v>
-      </c>
-      <c r="J96" t="n">
-        <v>1661785637000</v>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>19/02/15</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>29/08/22</t>
+        </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -9721,8 +9927,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I97" t="n">
-        <v>1263423600000</v>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>13/01/10</t>
+        </is>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
@@ -9817,8 +10025,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I98" t="n">
-        <v>1263423600000</v>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>13/01/10</t>
+        </is>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
@@ -9913,8 +10123,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I99" t="n">
-        <v>1213653600000</v>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>16/06/08</t>
+        </is>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
@@ -10009,8 +10221,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I100" t="n">
-        <v>1213653600000</v>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>16/06/08</t>
+        </is>
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
@@ -10105,11 +10319,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I101" t="n">
-        <v>1073862000000</v>
-      </c>
-      <c r="J101" t="n">
-        <v>1640075969000</v>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>11/01/04</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>21/12/21</t>
+        </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -10203,8 +10421,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I102" t="n">
-        <v>996703200000</v>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>01/08/01</t>
+        </is>
       </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
@@ -10299,8 +10519,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I103" t="n">
-        <v>996703200000</v>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>01/08/01</t>
+        </is>
       </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
@@ -10395,8 +10617,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I104" t="n">
-        <v>1248386400000</v>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>23/07/09</t>
+        </is>
       </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
@@ -10491,8 +10715,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I105" t="n">
-        <v>1248300000000</v>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>22/07/09</t>
+        </is>
       </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
@@ -10587,8 +10813,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I106" t="n">
-        <v>867708000000</v>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>30/06/97</t>
+        </is>
       </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
@@ -10683,11 +10911,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I107" t="n">
-        <v>1144360800000</v>
-      </c>
-      <c r="J107" t="n">
-        <v>1730820306000</v>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>06/04/06</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>05/11/24</t>
+        </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -10781,11 +11013,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I108" t="n">
-        <v>1144360800000</v>
-      </c>
-      <c r="J108" t="n">
-        <v>1730820305000</v>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>06/04/06</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>05/11/24</t>
+        </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -10879,8 +11115,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I109" t="n">
-        <v>1202770800000</v>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>11/02/08</t>
+        </is>
       </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
@@ -10975,8 +11213,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I110" t="n">
-        <v>1202770800000</v>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>11/02/08</t>
+        </is>
       </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
@@ -11071,8 +11311,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I111" t="n">
-        <v>1183068000000</v>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>28/06/07</t>
+        </is>
       </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
@@ -11167,8 +11409,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I112" t="n">
-        <v>1183068000000</v>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>28/06/07</t>
+        </is>
       </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
@@ -11263,8 +11507,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I113" t="n">
-        <v>1291071600000</v>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>29/11/10</t>
+        </is>
       </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
@@ -11359,8 +11605,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I114" t="n">
-        <v>1216245600000</v>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>16/07/08</t>
+        </is>
       </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
@@ -11455,8 +11703,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I115" t="n">
-        <v>1216245600000</v>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>16/07/08</t>
+        </is>
       </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
@@ -11551,11 +11801,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I116" t="n">
-        <v>1300834800000</v>
-      </c>
-      <c r="J116" t="n">
-        <v>1731320161000</v>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>22/03/11</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>11/11/24</t>
+        </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -11649,11 +11903,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I117" t="n">
-        <v>1300834800000</v>
-      </c>
-      <c r="J117" t="n">
-        <v>1729003024000</v>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>22/03/11</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>15/10/24</t>
+        </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -11747,8 +12005,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I118" t="n">
-        <v>1295996400000</v>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>25/01/11</t>
+        </is>
       </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
@@ -11843,8 +12103,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I119" t="n">
-        <v>1295996400000</v>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>25/01/11</t>
+        </is>
       </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
@@ -11939,8 +12201,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I120" t="n">
-        <v>1296082800000</v>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>26/01/11</t>
+        </is>
       </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
@@ -12035,8 +12299,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I121" t="n">
-        <v>1296082800000</v>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>26/01/11</t>
+        </is>
       </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
@@ -12131,11 +12397,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I122" t="n">
-        <v>1114725600000</v>
-      </c>
-      <c r="J122" t="n">
-        <v>1637593801000</v>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>28/04/05</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>22/11/21</t>
+        </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -12143,7 +12413,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
         <v>1</v>
@@ -12229,11 +12499,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I123" t="n">
-        <v>1075935600000</v>
-      </c>
-      <c r="J123" t="n">
-        <v>1637593802000</v>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>04/02/04</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>22/11/21</t>
+        </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -12241,7 +12515,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
         <v>1</v>
@@ -12327,8 +12601,10 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I124" t="n">
-        <v>1349871741000</v>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>10/10/12</t>
+        </is>
       </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
@@ -12423,11 +12699,15 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I125" t="n">
-        <v>880930800000</v>
-      </c>
-      <c r="J125" t="n">
-        <v>1636995048000</v>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>30/11/97</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>15/11/21</t>
+        </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -12521,8 +12801,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I126" t="n">
-        <v>1460477260000</v>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>12/04/16</t>
+        </is>
       </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
@@ -12617,8 +12899,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I127" t="n">
-        <v>1460477259000</v>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>12/04/16</t>
+        </is>
       </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
@@ -12713,8 +12997,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I128" t="n">
-        <v>1460477258000</v>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>12/04/16</t>
+        </is>
       </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
@@ -12809,11 +13095,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I129" t="n">
-        <v>1485471600000</v>
-      </c>
-      <c r="J129" t="n">
-        <v>1660205385000</v>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>26/01/17</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>11/08/22</t>
+        </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -12907,11 +13197,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I130" t="n">
-        <v>1485471600000</v>
-      </c>
-      <c r="J130" t="n">
-        <v>1660205588000</v>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>26/01/17</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>11/08/22</t>
+        </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -13005,11 +13299,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I131" t="n">
-        <v>1485471600000</v>
-      </c>
-      <c r="J131" t="n">
-        <v>1660205308000</v>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>26/01/17</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>11/08/22</t>
+        </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -13103,8 +13401,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I132" t="n">
-        <v>1449840583000</v>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>11/12/15</t>
+        </is>
       </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
@@ -13199,8 +13499,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I133" t="n">
-        <v>1449840594000</v>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>11/12/15</t>
+        </is>
       </c>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
@@ -13295,8 +13597,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I134" t="n">
-        <v>1479285533000</v>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>16/11/16</t>
+        </is>
       </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
@@ -13391,8 +13695,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I135" t="n">
-        <v>1479250800000</v>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>15/11/16</t>
+        </is>
       </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
@@ -13487,8 +13793,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I136" t="n">
-        <v>1479285514000</v>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>16/11/16</t>
+        </is>
       </c>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
@@ -13583,8 +13891,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I137" t="n">
-        <v>1479285505000</v>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>16/11/16</t>
+        </is>
       </c>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
@@ -13679,11 +13989,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I138" t="n">
-        <v>1452770176000</v>
-      </c>
-      <c r="J138" t="n">
-        <v>1659948764000</v>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>14/01/16</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>08/08/22</t>
+        </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -13777,11 +14091,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I139" t="n">
-        <v>1452770182000</v>
-      </c>
-      <c r="J139" t="n">
-        <v>1659948770000</v>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>14/01/16</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>08/08/22</t>
+        </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -13875,11 +14193,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I140" t="n">
-        <v>1452770180000</v>
-      </c>
-      <c r="J140" t="n">
-        <v>1659948776000</v>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>14/01/16</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>08/08/22</t>
+        </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -13973,11 +14295,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I141" t="n">
-        <v>1452770179000</v>
-      </c>
-      <c r="J141" t="n">
-        <v>1659948776000</v>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>14/01/16</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>08/08/22</t>
+        </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -14071,8 +14397,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I142" t="n">
-        <v>899244000000</v>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>30/06/98</t>
+        </is>
       </c>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
@@ -14167,8 +14495,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I143" t="n">
-        <v>899244000000</v>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>30/06/98</t>
+        </is>
       </c>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
@@ -14263,8 +14593,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I144" t="n">
-        <v>899244000000</v>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>30/06/98</t>
+        </is>
       </c>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
@@ -14359,8 +14691,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I145" t="n">
-        <v>1273615200000</v>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>11/05/10</t>
+        </is>
       </c>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
@@ -14455,8 +14789,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I146" t="n">
-        <v>1273615200000</v>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>11/05/10</t>
+        </is>
       </c>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
@@ -14551,8 +14887,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I147" t="n">
-        <v>1273615200000</v>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>11/05/10</t>
+        </is>
       </c>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
@@ -14647,8 +14985,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I148" t="n">
-        <v>1273615200000</v>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>11/05/10</t>
+        </is>
       </c>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
@@ -14743,8 +15083,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I149" t="n">
-        <v>1392228617000</v>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>12/02/14</t>
+        </is>
       </c>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
@@ -14839,8 +15181,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I150" t="n">
-        <v>728521200000</v>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>31/01/93</t>
+        </is>
       </c>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
@@ -14935,8 +15279,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I151" t="n">
-        <v>678319200000</v>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>30/06/91</t>
+        </is>
       </c>
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
@@ -15031,8 +15377,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I152" t="n">
-        <v>678319200000</v>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>30/06/91</t>
+        </is>
       </c>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
@@ -15127,8 +15475,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I153" t="n">
-        <v>1288738800000</v>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>02/11/10</t>
+        </is>
       </c>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
@@ -15223,8 +15573,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I154" t="n">
-        <v>1288738800000</v>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>02/11/10</t>
+        </is>
       </c>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
@@ -15303,7 +15655,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Guidotti Farma S.L.</t>
+          <t>Laboratorios Menarini S.A.</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -15319,8 +15671,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I155" t="n">
-        <v>1248127200000</v>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>20/07/09</t>
+        </is>
       </c>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
@@ -15399,7 +15753,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Guidotti Farma S.L.</t>
+          <t>Laboratorios Menarini S.A.</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -15415,8 +15769,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I156" t="n">
-        <v>1248127200000</v>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>20/07/09</t>
+        </is>
       </c>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
@@ -15495,7 +15851,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Guidotti Farma S.L.</t>
+          <t>Laboratorios Menarini S.A.</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -15511,8 +15867,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I157" t="n">
-        <v>950050800000</v>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>08/02/00</t>
+        </is>
       </c>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
@@ -15607,8 +15965,10 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I158" t="n">
-        <v>1437516000000</v>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>21/07/15</t>
+        </is>
       </c>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
@@ -15703,8 +16063,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I159" t="n">
-        <v>1308607200000</v>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>20/06/11</t>
+        </is>
       </c>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
@@ -15799,8 +16161,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I160" t="n">
-        <v>1308607200000</v>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>20/06/11</t>
+        </is>
       </c>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
@@ -15895,8 +16259,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I161" t="n">
-        <v>1308607200000</v>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>20/06/11</t>
+        </is>
       </c>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
@@ -15991,8 +16357,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I162" t="n">
-        <v>1352191158000</v>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>06/11/12</t>
+        </is>
       </c>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
@@ -16087,8 +16455,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I163" t="n">
-        <v>1352191156000</v>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>06/11/12</t>
+        </is>
       </c>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
@@ -16183,8 +16553,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I164" t="n">
-        <v>1334440800000</v>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>14/04/12</t>
+        </is>
       </c>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
@@ -16279,11 +16651,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I165" t="n">
-        <v>1383079311000</v>
-      </c>
-      <c r="J165" t="n">
-        <v>1678703511000</v>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>29/10/13</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>13/03/23</t>
+        </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -16377,11 +16753,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I166" t="n">
-        <v>1383079304000</v>
-      </c>
-      <c r="J166" t="n">
-        <v>1678703520000</v>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>29/10/13</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>13/03/23</t>
+        </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
@@ -16475,8 +16855,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I167" t="n">
-        <v>197157600000</v>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>31/03/76</t>
+        </is>
       </c>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
@@ -16571,8 +16953,10 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I168" t="n">
-        <v>323391600000</v>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>31/03/80</t>
+        </is>
       </c>
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
@@ -16667,8 +17051,10 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I169" t="n">
-        <v>323391600000</v>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>31/03/80</t>
+        </is>
       </c>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
@@ -16763,8 +17149,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I170" t="n">
-        <v>1133391600000</v>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>30/11/05</t>
+        </is>
       </c>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
@@ -16859,8 +17247,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I171" t="n">
-        <v>1133391600000</v>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>30/11/05</t>
+        </is>
       </c>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
@@ -16955,8 +17345,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I172" t="n">
-        <v>1133391600000</v>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>30/11/05</t>
+        </is>
       </c>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
@@ -17051,8 +17443,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I173" t="n">
-        <v>1095285600000</v>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>15/09/04</t>
+        </is>
       </c>
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
@@ -17147,8 +17541,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I174" t="n">
-        <v>1095285600000</v>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>15/09/04</t>
+        </is>
       </c>
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
@@ -17243,8 +17639,10 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I175" t="n">
-        <v>833580000000</v>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>31/05/96</t>
+        </is>
       </c>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
@@ -17339,8 +17737,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I176" t="n">
-        <v>1010012400000</v>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>02/01/02</t>
+        </is>
       </c>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
@@ -17435,8 +17835,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I177" t="n">
-        <v>1193004000000</v>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>21/10/07</t>
+        </is>
       </c>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
@@ -17531,8 +17933,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I178" t="n">
-        <v>1010012400000</v>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>02/01/02</t>
+        </is>
       </c>
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
@@ -17627,8 +18031,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I179" t="n">
-        <v>1276725600000</v>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>16/06/10</t>
+        </is>
       </c>
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
@@ -17723,8 +18129,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I180" t="n">
-        <v>1295564400000</v>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>20/01/11</t>
+        </is>
       </c>
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
@@ -17819,8 +18227,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I181" t="n">
-        <v>1276725600000</v>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>16/06/10</t>
+        </is>
       </c>
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
@@ -17915,8 +18325,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I182" t="n">
-        <v>1289948400000</v>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>16/11/10</t>
+        </is>
       </c>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
@@ -18011,8 +18423,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I183" t="n">
-        <v>1289948400000</v>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>16/11/10</t>
+        </is>
       </c>
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
@@ -18107,8 +18521,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I184" t="n">
-        <v>1295910000000</v>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>24/01/11</t>
+        </is>
       </c>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
@@ -18203,8 +18619,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I185" t="n">
-        <v>1295910000000</v>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>24/01/11</t>
+        </is>
       </c>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
@@ -18299,8 +18717,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I186" t="n">
-        <v>1325026800000</v>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>27/12/11</t>
+        </is>
       </c>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
@@ -18395,8 +18815,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I187" t="n">
-        <v>1325026800000</v>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>27/12/11</t>
+        </is>
       </c>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
@@ -18491,8 +18913,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I188" t="n">
-        <v>1295910000000</v>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>24/01/11</t>
+        </is>
       </c>
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
@@ -18587,8 +19011,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I189" t="n">
-        <v>441759600000</v>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>31/12/83</t>
+        </is>
       </c>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
@@ -18683,8 +19109,10 @@
           <t>CAPSULA</t>
         </is>
       </c>
-      <c r="I190" t="n">
-        <v>644191200000</v>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>31/05/90</t>
+        </is>
       </c>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
@@ -18779,8 +19207,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I191" t="n">
-        <v>1436824800000</v>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>13/07/15</t>
+        </is>
       </c>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
@@ -18875,8 +19305,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I192" t="n">
-        <v>1436824800000</v>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>13/07/15</t>
+        </is>
       </c>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
@@ -18971,8 +19403,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I193" t="n">
-        <v>1140044400000</v>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>15/02/06</t>
+        </is>
       </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
@@ -19067,8 +19501,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I194" t="n">
-        <v>1213740000000</v>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>17/06/08</t>
+        </is>
       </c>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
@@ -19163,8 +19599,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I195" t="n">
-        <v>1213740000000</v>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>17/06/08</t>
+        </is>
       </c>
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
@@ -19259,8 +19697,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I196" t="n">
-        <v>1416351600000</v>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>18/11/14</t>
+        </is>
       </c>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
@@ -19355,8 +19795,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I197" t="n">
-        <v>730940400000</v>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>28/02/93</t>
+        </is>
       </c>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
@@ -19447,8 +19889,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I198" t="n">
-        <v>796687200000</v>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>31/03/95</t>
+        </is>
       </c>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
@@ -19539,8 +19983,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I199" t="n">
-        <v>1038956400000</v>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>03/12/02</t>
+        </is>
       </c>
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
@@ -19631,8 +20077,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I200" t="n">
-        <v>715298400000</v>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>31/08/92</t>
+        </is>
       </c>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
@@ -19723,8 +20171,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I201" t="n">
-        <v>715298400000</v>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>31/08/92</t>
+        </is>
       </c>
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
